--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486813_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486813_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0194</v>
+        <v>2.0748</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9611</v>
+        <v>4.1407</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9417</v>
+        <v>-2.0658</v>
       </c>
       <c r="G2" t="n">
         <v>1.1398</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>2.096</v>
+        <v>1.1514</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7648</v>
+        <v>0.9443</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3313</v>
+        <v>0.2071</v>
       </c>
       <c r="V2" t="n">
         <v>0.9421</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0963</v>
+        <v>0.5432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.484</v>
+        <v>-0.739</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5803</v>
+        <v>1.2823</v>
       </c>
       <c r="G3" t="n">
         <v>0.1364</v>
@@ -688,13 +688,13 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9599</v>
+        <v>0.4069</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.3382</v>
       </c>
       <c r="U3" t="n">
-        <v>1.043</v>
+        <v>0.745</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.646</v>
+        <v>-0.1356</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3645</v>
+        <v>0.6266</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0105</v>
+        <v>-0.7622</v>
       </c>
       <c r="G4" t="n">
         <v>1.2396</v>
@@ -766,13 +766,13 @@
         <v>0.3862</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8276</v>
+        <v>-0.3173</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9933</v>
+        <v>-0.7313</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1657</v>
+        <v>0.414</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2856</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2188</v>
+        <v>-2.2119</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9255</v>
+        <v>-0.9186</v>
       </c>
       <c r="F5" t="n">
         <v>-1.2933</v>
@@ -844,10 +844,10 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1654</v>
+        <v>0.1724</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3031</v>
+        <v>0.31</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1377</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.4977</v>
+        <v>-3.3942</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0823</v>
+        <v>1.1857</v>
       </c>
       <c r="F6" t="n">
         <v>-4.58</v>
@@ -922,10 +922,10 @@
         <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0827</v>
+        <v>0.1861</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1932</v>
+        <v>-0.0898</v>
       </c>
       <c r="U6" t="n">
         <v>0.2759</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.7132</v>
+        <v>-3.4553</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0272</v>
+        <v>-2.8686</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.5867</v>
       </c>
       <c r="G7" t="n">
         <v>-2.5381</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2097</v>
+        <v>0.0482</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5518</v>
+        <v>-0.3932</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3421</v>
+        <v>0.4415</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9331</v>
+        <v>-3.4779</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6497</v>
+        <v>-2.4428</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2834</v>
+        <v>-1.0351</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3537</v>
@@ -1078,13 +1078,13 @@
         <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7724</v>
+        <v>-0.3173</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5243</v>
+        <v>-0.3174</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2481</v>
+        <v>0.0002</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7748</v>
+        <v>-4.2385</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1188</v>
+        <v>-3.9894</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.656</v>
+        <v>-0.2491</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5955</v>
+        <v>-4.5102</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3238</v>
+        <v>-0.9792</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9193</v>
+        <v>-3.5311</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.243</v>
+        <v>-3.0748</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0139</v>
+        <v>0.3319</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2569</v>
+        <v>-3.4067</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3525</v>
+        <v>-1.4354</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6901</v>
+        <v>-1.311</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6624</v>
+        <v>-0.1244</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9654</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3515</v>
+        <v>-1.5446</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7006</v>
+        <v>0.5654</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5243</v>
+        <v>0.3445</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1763</v>
+        <v>0.2209</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0049</v>
+        <v>-4.3156</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8895</v>
+        <v>-1.8085</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1154</v>
+        <v>-2.507</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2837</v>
+        <v>-1.5955</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2687</v>
+        <v>0.3238</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.015</v>
+        <v>-1.9193</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4137</v>
+        <v>-0.243</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3369</v>
+        <v>1.0139</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-1.2569</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.87</v>
+        <v>-1.3525</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9318</v>
+        <v>-0.6901</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9382</v>
+        <v>-0.6624</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3169</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4754</v>
+        <v>-1.3515</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5957</v>
+        <v>-0.2414</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3858</v>
+        <v>-0.214</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2099</v>
+        <v>-0.0274</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6138</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.019</v>
+        <v>-4.6166</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7203</v>
+        <v>-3.1881</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2988</v>
+        <v>-1.4284</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.5102</v>
+        <v>-4.4938</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9792</v>
+        <v>-1.8692</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.5311</v>
+        <v>-2.6246</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0748</v>
+        <v>-1.6309</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3319</v>
+        <v>-0.2136</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.4067</v>
+        <v>-1.4174</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4354</v>
+        <v>-2.8629</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.311</v>
+        <v>-1.6557</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1244</v>
+        <v>-1.2072</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5446</v>
+        <v>-1.1585</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2152</v>
+        <v>0.2481</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3864</v>
+        <v>-0.0279</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1712</v>
+        <v>0.276</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1958</v>
+        <v>-4.8905</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7674</v>
+        <v>-2.6757</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4284</v>
+        <v>-2.2148</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.4938</v>
+        <v>-3.2837</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8692</v>
+        <v>-2.2687</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6246</v>
+        <v>-1.015</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6309</v>
+        <v>-0.4137</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2136</v>
+        <v>-0.3369</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4174</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8629</v>
+        <v>-2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6557</v>
+        <v>-1.9318</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2072</v>
+        <v>-0.9382</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1585</v>
+        <v>-3.4754</v>
       </c>
       <c r="R12" t="n">
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3311</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6071</v>
+        <v>0.5996</v>
       </c>
       <c r="U12" t="n">
-        <v>0.276</v>
+        <v>0.1106</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3709</v>
+        <v>0.6138</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3708</v>
+        <v>-7.3127</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2155</v>
+        <v>-4.8843</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1553</v>
+        <v>-2.4284</v>
       </c>
       <c r="G13" t="n">
         <v>-4.2905</v>
@@ -1468,13 +1468,13 @@
         <v>0.3862</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2246</v>
+        <v>0.2827</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4409</v>
+        <v>-0.2279</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1118</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.2584</v>
+        <v>-35.4308</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.39</v>
+        <v>-17.562</v>
       </c>
       <c r="F14" t="n">
         <v>-17.8685</v>
@@ -1519,7 +1519,7 @@
         <v>-17.0678</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.611000000000001</v>
+        <v>-4.611000000000002</v>
       </c>
       <c r="K14" t="n">
         <v>3.798</v>
@@ -1546,13 +1546,13 @@
         <v>7.7235</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0677</v>
+        <v>2.8954</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9689000000000001</v>
+        <v>-0.1412999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0368</v>
+        <v>3.0367</v>
       </c>
       <c r="V14" t="n">
         <v>-6.223700000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.624499999999999</v>
+        <v>9.3306</v>
       </c>
       <c r="E15" t="n">
-        <v>8.231199999999999</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3933</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>8.916700000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2576</v>
+        <v>-0.5515</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8277</v>
+        <v>-0.6209</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4299</v>
+        <v>0.0694</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.331200000000001</v>
+        <v>8.7241</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1104</v>
+        <v>4.2138</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2208</v>
+        <v>4.5103</v>
       </c>
       <c r="G16" t="n">
         <v>6.251</v>
@@ -1702,13 +1702,13 @@
         <v>2.7031</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.055</v>
+        <v>0.3379</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4142</v>
+        <v>-0.3107</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3592</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>1.5559</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0278</v>
+        <v>5.414</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3477</v>
+        <v>0.8305</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6801</v>
+        <v>4.5834</v>
       </c>
       <c r="G17" t="n">
         <v>3.4635</v>
@@ -1780,13 +1780,13 @@
         <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5449</v>
+        <v>0.9311</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3857</v>
+        <v>-0.1314</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1592</v>
+        <v>1.0626</v>
       </c>
       <c r="V17" t="n">
         <v>1.5985</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.0027</v>
+        <v>5.0743</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9984</v>
+        <v>3.2052</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0043</v>
+        <v>1.869</v>
       </c>
       <c r="G18" t="n">
         <v>3.211</v>
@@ -1858,13 +1858,13 @@
         <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1817</v>
+        <v>-0.1102</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9381</v>
+        <v>-0.7313</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7564</v>
+        <v>0.6211</v>
       </c>
       <c r="V18" t="n">
         <v>0.0426</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2526</v>
+        <v>3.5968</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4878</v>
+        <v>1.3015</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7648</v>
+        <v>2.2953</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4669</v>
+        <v>-0.3687</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4342</v>
+        <v>-1.5172</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9012</v>
+        <v>1.1484</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.229</v>
+        <v>-0.3191</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8823</v>
+        <v>-0.8956</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6534</v>
+        <v>0.5766</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6959</v>
+        <v>-0.0497</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2478</v>
+        <v>0.5719</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>2.3169</v>
       </c>
       <c r="S19" t="n">
-        <v>1.048</v>
+        <v>-0.6137</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7168</v>
+        <v>-0.6417</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3312</v>
+        <v>0.028</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4673</v>
+        <v>3.027</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7844</v>
+        <v>0.9731</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6829</v>
+        <v>2.0539</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3687</v>
+        <v>3.6968</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5172</v>
+        <v>2.9937</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1484</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3191</v>
+        <v>3.0501</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8956</v>
+        <v>3.2014</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5766</v>
+        <v>-0.1513</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0497</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.2077</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5719</v>
+        <v>0.8544</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1239</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1931</v>
+        <v>-2.1239</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3169</v>
+        <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7432</v>
+        <v>-0.4688</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1588</v>
+        <v>-0.5244</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5843</v>
+        <v>0.0557</v>
       </c>
       <c r="V20" t="n">
-        <v>2.4554</v>
+        <v>0.5712</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4554</v>
+        <v>0.5712</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0395</v>
+        <v>2.77</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5594</v>
+        <v>-0.1327</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4802</v>
+        <v>2.9027</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6968</v>
+        <v>0.4669</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9937</v>
+        <v>-1.4342</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.9012</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0501</v>
+        <v>-0.229</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2014</v>
+        <v>-0.8823</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1513</v>
+        <v>0.6534</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6959</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2077</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8544</v>
+        <v>1.2478</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4562</v>
+        <v>0.5653</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9381</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5181</v>
+        <v>0.4691</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5127</v>
+        <v>0.39</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.961</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1634</v>
+        <v>1.3509</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2926</v>
@@ -2170,13 +2170,13 @@
         <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>0.033</v>
+        <v>-0.0897</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1377</v>
+        <v>-0.1726</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1047</v>
+        <v>0.0829</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>36.2583</v>
+        <v>38.3268</v>
       </c>
       <c r="E23" t="n">
-        <v>17.8686</v>
+        <v>17.8684</v>
       </c>
       <c r="F23" t="n">
-        <v>18.3898</v>
+        <v>20.4581</v>
       </c>
       <c r="G23" t="n">
         <v>25.3446</v>
@@ -2242,19 +2242,19 @@
         <v>6.7578</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.723299999999998</v>
+        <v>-7.723299999999999</v>
       </c>
       <c r="R23" t="n">
         <v>14.4808</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0678</v>
+        <v>0.000400000000000067</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0367</v>
+        <v>-3.0368</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9689999999999999</v>
+        <v>3.0375</v>
       </c>
       <c r="V23" t="n">
         <v>6.2236</v>
